--- a/assets/Student.xlsx
+++ b/assets/Student.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\School Attendance\school_attendance\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821FAAAA-6BA0-4279-B917-477B6506CC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A45E41-B776-41C7-ABD8-388D0166DE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{D5E02D08-188B-44BA-B1CD-54EC824D01E7}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>username</t>
   </si>
@@ -92,6 +92,18 @@
   </si>
   <si>
     <t>class_id</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>father_name</t>
+  </si>
+  <si>
+    <t>route</t>
   </si>
 </sst>
 </file>
@@ -487,7 +499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A4C1696-742D-4934-8472-4E16B1B4E922}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -499,9 +511,10 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" customWidth="1"/>
     <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,8 +539,18 @@
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="6">
